--- a/public/downloads/customer/customer_import_template_v1.xlsx
+++ b/public/downloads/customer/customer_import_template_v1.xlsx
@@ -1648,7 +1648,7 @@
       <formula1>"Facebook,Instagram,Google,Giới thiệu từ khách cũ,Trang web,Tự tìm kiếm,Tổng đài,Môi giới,Dữ liệu bán hàng"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="N2:N4">
-      <formula1>"Khách hàng trung thành,Khách hàng cũ,Khách hàng tiềm năng,Khách vãng lai,Khách hàng tiềm năng mới,Khách hàng dang chăm sóc,VIP,VVIP"</formula1>
+      <formula1>"Khách hàng trung thành,Khách hàng cũ,Khách hàng tiềm năng,Khách vãng lai,Khách hàng tiềm năng mới,Khách hàng đang chăm sóc,VIP,VVIP"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="L2:L4">
       <formula1>"Cá nhân,Tổ chức"</formula1>
